--- a/output/yearly_total_coral_cover_iteration_79_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_79_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.246737544858191</v>
+        <v>1.279635910427501</v>
       </c>
       <c r="C3" t="n">
-        <v>4.663327993420526</v>
+        <v>4.612502914771668</v>
       </c>
       <c r="D3" t="n">
-        <v>6.09163169780011</v>
+        <v>6.241819461595787</v>
       </c>
       <c r="E3" t="n">
-        <v>12.00169723607883</v>
+        <v>12.13395828679496</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.355398268527335</v>
+        <v>1.451351304233539</v>
       </c>
       <c r="C4" t="n">
-        <v>5.236717514887625</v>
+        <v>5.061406215439734</v>
       </c>
       <c r="D4" t="n">
-        <v>6.312622993551833</v>
+        <v>6.549093901913649</v>
       </c>
       <c r="E4" t="n">
-        <v>12.90473877696679</v>
+        <v>13.06185142158692</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.50089426477787</v>
+        <v>1.678240397960006</v>
       </c>
       <c r="C5" t="n">
-        <v>6.006638578828438</v>
+        <v>5.596566103115284</v>
       </c>
       <c r="D5" t="n">
-        <v>6.586583758785512</v>
+        <v>6.927758816973929</v>
       </c>
       <c r="E5" t="n">
-        <v>14.09411660239182</v>
+        <v>14.20256531804922</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.660236105223516</v>
+        <v>1.942476081164507</v>
       </c>
       <c r="C6" t="n">
-        <v>6.945450633739305</v>
+        <v>6.236045044627214</v>
       </c>
       <c r="D6" t="n">
-        <v>6.868017963980866</v>
+        <v>7.294007442442369</v>
       </c>
       <c r="E6" t="n">
-        <v>15.47370470294369</v>
+        <v>15.47252856823409</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.839139272529905</v>
+        <v>2.243925186411146</v>
       </c>
       <c r="C7" t="n">
-        <v>8.019725777632742</v>
+        <v>7.022243547975812</v>
       </c>
       <c r="D7" t="n">
-        <v>7.147984567648578</v>
+        <v>7.761489031490532</v>
       </c>
       <c r="E7" t="n">
-        <v>17.00684961781122</v>
+        <v>17.02765776587749</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.076220054390893</v>
+        <v>1.440913874603532</v>
       </c>
       <c r="C8" t="n">
-        <v>5.597273274529656</v>
+        <v>4.705564795907882</v>
       </c>
       <c r="D8" t="n">
-        <v>5.300918961371544</v>
+        <v>5.985332147494192</v>
       </c>
       <c r="E8" t="n">
-        <v>11.97441229029209</v>
+        <v>12.1318108180056</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.331715367330244</v>
+        <v>1.821998825118506</v>
       </c>
       <c r="C9" t="n">
-        <v>6.819649455653722</v>
+        <v>5.782862058000323</v>
       </c>
       <c r="D9" t="n">
-        <v>5.727479880880652</v>
+        <v>6.498634330174293</v>
       </c>
       <c r="E9" t="n">
-        <v>13.87884470386462</v>
+        <v>14.10349521329312</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.593481436004031</v>
+        <v>2.229092156465532</v>
       </c>
       <c r="C10" t="n">
-        <v>8.195867617385197</v>
+        <v>7.019397461187537</v>
       </c>
       <c r="D10" t="n">
-        <v>6.124626676183327</v>
+        <v>7.027507438926726</v>
       </c>
       <c r="E10" t="n">
-        <v>15.91397572957256</v>
+        <v>16.27599705657979</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.858846816688863</v>
+        <v>2.644663277566712</v>
       </c>
       <c r="C11" t="n">
-        <v>9.711580152624514</v>
+        <v>8.370012000166991</v>
       </c>
       <c r="D11" t="n">
-        <v>6.529570424505319</v>
+        <v>7.485023071199973</v>
       </c>
       <c r="E11" t="n">
-        <v>18.0999973938187</v>
+        <v>18.49969834893368</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.124903799414469</v>
+        <v>3.071713443548398</v>
       </c>
       <c r="C12" t="n">
-        <v>11.33294469539295</v>
+        <v>9.793415262449177</v>
       </c>
       <c r="D12" t="n">
-        <v>6.947206704755575</v>
+        <v>7.973795914291019</v>
       </c>
       <c r="E12" t="n">
-        <v>20.40505519956299</v>
+        <v>20.83892462028859</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.387707570854355</v>
+        <v>3.492593131761737</v>
       </c>
       <c r="C13" t="n">
-        <v>13.102092748734</v>
+        <v>11.24090082632765</v>
       </c>
       <c r="D13" t="n">
-        <v>7.290302550668003</v>
+        <v>8.47494215122836</v>
       </c>
       <c r="E13" t="n">
-        <v>22.78010287025636</v>
+        <v>23.20843610931775</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.388672310180071</v>
+        <v>2.020309148138383</v>
       </c>
       <c r="C14" t="n">
-        <v>9.363300919529443</v>
+        <v>7.8308222056313</v>
       </c>
       <c r="D14" t="n">
-        <v>5.553972564896182</v>
+        <v>6.363688618927824</v>
       </c>
       <c r="E14" t="n">
-        <v>16.3059457946057</v>
+        <v>16.21481997269751</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.403329803404476</v>
+        <v>2.097435247784013</v>
       </c>
       <c r="C15" t="n">
-        <v>10.20260684936708</v>
+        <v>8.447006334724769</v>
       </c>
       <c r="D15" t="n">
-        <v>5.498199477817922</v>
+        <v>6.380918291137356</v>
       </c>
       <c r="E15" t="n">
-        <v>17.10413613058948</v>
+        <v>16.92535987364614</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.609261201847287</v>
+        <v>2.461104049868159</v>
       </c>
       <c r="C16" t="n">
-        <v>12.17612590192107</v>
+        <v>9.970236985248908</v>
       </c>
       <c r="D16" t="n">
-        <v>5.824218255444203</v>
+        <v>6.829665349271531</v>
       </c>
       <c r="E16" t="n">
-        <v>19.60960535921255</v>
+        <v>19.2610063843886</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.27589895139324</v>
+        <v>1.989177928436717</v>
       </c>
       <c r="C17" t="n">
-        <v>11.28782094416447</v>
+        <v>9.207811718130836</v>
       </c>
       <c r="D17" t="n">
-        <v>5.321867772658152</v>
+        <v>6.342649765625817</v>
       </c>
       <c r="E17" t="n">
-        <v>17.88558766821586</v>
+        <v>17.53963941219337</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.447135385967969</v>
+        <v>2.293627709000696</v>
       </c>
       <c r="C18" t="n">
-        <v>13.27949251176997</v>
+        <v>10.71168230392722</v>
       </c>
       <c r="D18" t="n">
-        <v>5.626317553222131</v>
+        <v>6.755081976179901</v>
       </c>
       <c r="E18" t="n">
-        <v>20.35294545096007</v>
+        <v>19.76039198910782</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.441568876484889</v>
+        <v>2.324660753931937</v>
       </c>
       <c r="C19" t="n">
-        <v>14.29208672888422</v>
+        <v>11.43955005185581</v>
       </c>
       <c r="D19" t="n">
-        <v>5.646737905470465</v>
+        <v>6.844794081393975</v>
       </c>
       <c r="E19" t="n">
-        <v>21.38039351083957</v>
+        <v>20.60900488718173</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.598835041228186</v>
+        <v>2.614305779115874</v>
       </c>
       <c r="C20" t="n">
-        <v>16.43168804056563</v>
+        <v>13.15671514387687</v>
       </c>
       <c r="D20" t="n">
-        <v>5.927871178058581</v>
+        <v>7.282516112809458</v>
       </c>
       <c r="E20" t="n">
-        <v>23.95839425985239</v>
+        <v>23.0535370358022</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9500176184455534</v>
+        <v>1.570197460695306</v>
       </c>
       <c r="C21" t="n">
-        <v>12.07070583343904</v>
+        <v>9.671019919948565</v>
       </c>
       <c r="D21" t="n">
-        <v>4.883723589729843</v>
+        <v>6.04592633949426</v>
       </c>
       <c r="E21" t="n">
-        <v>17.90444704161444</v>
+        <v>17.28714372013813</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_79_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_79_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.279635910427501</v>
+        <v>1.254100652640042</v>
       </c>
       <c r="C3" t="n">
-        <v>4.612502914771668</v>
+        <v>4.621358279063974</v>
       </c>
       <c r="D3" t="n">
-        <v>6.241819461595787</v>
+        <v>6.10853739326724</v>
       </c>
       <c r="E3" t="n">
-        <v>12.13395828679496</v>
+        <v>11.98399632497125</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.451351304233539</v>
+        <v>1.376489246203281</v>
       </c>
       <c r="C4" t="n">
-        <v>5.061406215439734</v>
+        <v>5.091061690060683</v>
       </c>
       <c r="D4" t="n">
-        <v>6.549093901913649</v>
+        <v>6.428587389670257</v>
       </c>
       <c r="E4" t="n">
-        <v>13.06185142158692</v>
+        <v>12.89613832593422</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.678240397960006</v>
+        <v>1.545814336957299</v>
       </c>
       <c r="C5" t="n">
-        <v>5.596566103115284</v>
+        <v>5.667110035059255</v>
       </c>
       <c r="D5" t="n">
-        <v>6.927758816973929</v>
+        <v>6.728211759381238</v>
       </c>
       <c r="E5" t="n">
-        <v>14.20256531804922</v>
+        <v>13.94113613139779</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.942476081164507</v>
+        <v>1.735179082636383</v>
       </c>
       <c r="C6" t="n">
-        <v>6.236045044627214</v>
+        <v>6.349050064622372</v>
       </c>
       <c r="D6" t="n">
-        <v>7.294007442442369</v>
+        <v>7.094725124518438</v>
       </c>
       <c r="E6" t="n">
-        <v>15.47252856823409</v>
+        <v>15.17895427177719</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.243925186411146</v>
+        <v>1.942556267940392</v>
       </c>
       <c r="C7" t="n">
-        <v>7.022243547975812</v>
+        <v>7.176944790682441</v>
       </c>
       <c r="D7" t="n">
-        <v>7.761489031490532</v>
+        <v>7.50744631772268</v>
       </c>
       <c r="E7" t="n">
-        <v>17.02765776587749</v>
+        <v>16.62694737634551</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.440913874603532</v>
+        <v>1.164319950132225</v>
       </c>
       <c r="C8" t="n">
-        <v>4.705564795907882</v>
+        <v>4.865975087659282</v>
       </c>
       <c r="D8" t="n">
-        <v>5.985332147494192</v>
+        <v>5.703958993776727</v>
       </c>
       <c r="E8" t="n">
-        <v>12.1318108180056</v>
+        <v>11.73425403156823</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.821998825118506</v>
+        <v>1.444804755488094</v>
       </c>
       <c r="C9" t="n">
-        <v>5.782862058000323</v>
+        <v>5.994857205830871</v>
       </c>
       <c r="D9" t="n">
-        <v>6.498634330174293</v>
+        <v>6.298244368963784</v>
       </c>
       <c r="E9" t="n">
-        <v>14.10349521329312</v>
+        <v>13.73790633028275</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.229092156465532</v>
+        <v>1.745265856900517</v>
       </c>
       <c r="C10" t="n">
-        <v>7.019397461187537</v>
+        <v>7.312621598822995</v>
       </c>
       <c r="D10" t="n">
-        <v>7.027507438926726</v>
+        <v>6.818712190476057</v>
       </c>
       <c r="E10" t="n">
-        <v>16.27599705657979</v>
+        <v>15.87659964619957</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.644663277566712</v>
+        <v>2.043809517540981</v>
       </c>
       <c r="C11" t="n">
-        <v>8.370012000166991</v>
+        <v>8.780009438763026</v>
       </c>
       <c r="D11" t="n">
-        <v>7.485023071199973</v>
+        <v>7.365224125240915</v>
       </c>
       <c r="E11" t="n">
-        <v>18.49969834893368</v>
+        <v>18.18904308154492</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.071713443548398</v>
+        <v>2.35264578357677</v>
       </c>
       <c r="C12" t="n">
-        <v>9.793415262449177</v>
+        <v>10.32172208945266</v>
       </c>
       <c r="D12" t="n">
-        <v>7.973795914291019</v>
+        <v>7.992817101924273</v>
       </c>
       <c r="E12" t="n">
-        <v>20.83892462028859</v>
+        <v>20.6671849749537</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.492593131761737</v>
+        <v>2.657067113458278</v>
       </c>
       <c r="C13" t="n">
-        <v>11.24090082632765</v>
+        <v>11.90641691591894</v>
       </c>
       <c r="D13" t="n">
-        <v>8.47494215122836</v>
+        <v>8.475665969294457</v>
       </c>
       <c r="E13" t="n">
-        <v>23.20843610931775</v>
+        <v>23.03914999867167</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.020309148138383</v>
+        <v>1.544082971762341</v>
       </c>
       <c r="C14" t="n">
-        <v>7.8308222056313</v>
+        <v>8.317238923177426</v>
       </c>
       <c r="D14" t="n">
-        <v>6.363688618927824</v>
+        <v>6.438900310550173</v>
       </c>
       <c r="E14" t="n">
-        <v>16.21481997269751</v>
+        <v>16.30022220548994</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.097435247784013</v>
+        <v>1.581114495166531</v>
       </c>
       <c r="C15" t="n">
-        <v>8.447006334724769</v>
+        <v>9.006926502887852</v>
       </c>
       <c r="D15" t="n">
-        <v>6.380918291137356</v>
+        <v>6.491688884607524</v>
       </c>
       <c r="E15" t="n">
-        <v>16.92535987364614</v>
+        <v>17.07972988266191</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.461104049868159</v>
+        <v>1.836467073041126</v>
       </c>
       <c r="C16" t="n">
-        <v>9.970236985248908</v>
+        <v>10.70384795724734</v>
       </c>
       <c r="D16" t="n">
-        <v>6.829665349271531</v>
+        <v>6.955319237938081</v>
       </c>
       <c r="E16" t="n">
-        <v>19.2610063843886</v>
+        <v>19.49563426822655</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.989177928436717</v>
+        <v>1.472709913663598</v>
       </c>
       <c r="C17" t="n">
-        <v>9.207811718130836</v>
+        <v>9.963747632923837</v>
       </c>
       <c r="D17" t="n">
-        <v>6.342649765625817</v>
+        <v>6.456925198400145</v>
       </c>
       <c r="E17" t="n">
-        <v>17.53963941219337</v>
+        <v>17.89338274498758</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.293627709000696</v>
+        <v>1.676589459404533</v>
       </c>
       <c r="C18" t="n">
-        <v>10.71168230392722</v>
+        <v>11.72471830750838</v>
       </c>
       <c r="D18" t="n">
-        <v>6.755081976179901</v>
+        <v>6.923638239522035</v>
       </c>
       <c r="E18" t="n">
-        <v>19.76039198910782</v>
+        <v>20.32494600643495</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.324660753931937</v>
+        <v>1.676461832202981</v>
       </c>
       <c r="C19" t="n">
-        <v>11.43955005185581</v>
+        <v>12.65253861036092</v>
       </c>
       <c r="D19" t="n">
-        <v>6.844794081393975</v>
+        <v>7.036225066245061</v>
       </c>
       <c r="E19" t="n">
-        <v>20.60900488718173</v>
+        <v>21.36522550880896</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.614305779115874</v>
+        <v>1.859292707164865</v>
       </c>
       <c r="C20" t="n">
-        <v>13.15671514387687</v>
+        <v>14.58578637208669</v>
       </c>
       <c r="D20" t="n">
-        <v>7.282516112809458</v>
+        <v>7.575361635509238</v>
       </c>
       <c r="E20" t="n">
-        <v>23.0535370358022</v>
+        <v>24.0204407147608</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.570197460695306</v>
+        <v>1.101570011550134</v>
       </c>
       <c r="C21" t="n">
-        <v>9.671019919948565</v>
+        <v>10.74676014939996</v>
       </c>
       <c r="D21" t="n">
-        <v>6.04592633949426</v>
+        <v>6.340902254712257</v>
       </c>
       <c r="E21" t="n">
-        <v>17.28714372013813</v>
+        <v>18.18923241566236</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_79_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_79_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.254100652640042</v>
+        <v>2.587945375140376</v>
       </c>
       <c r="C3" t="n">
-        <v>4.621358279063974</v>
+        <v>7.715895988728675</v>
       </c>
       <c r="D3" t="n">
-        <v>6.10853739326724</v>
+        <v>8.152381653737724</v>
       </c>
       <c r="E3" t="n">
-        <v>11.98399632497125</v>
+        <v>18.45622301760677</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.376489246203281</v>
+        <v>1.072534599960746</v>
       </c>
       <c r="C4" t="n">
-        <v>5.091061690060683</v>
+        <v>4.521885255666309</v>
       </c>
       <c r="D4" t="n">
-        <v>6.428587389670257</v>
+        <v>5.723550158217551</v>
       </c>
       <c r="E4" t="n">
-        <v>12.89613832593422</v>
+        <v>11.3179700138446</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.545814336957299</v>
+        <v>1.17798403547468</v>
       </c>
       <c r="C5" t="n">
-        <v>5.667110035059255</v>
+        <v>5.185061869803228</v>
       </c>
       <c r="D5" t="n">
-        <v>6.728211759381238</v>
+        <v>5.996420231450932</v>
       </c>
       <c r="E5" t="n">
-        <v>13.94113613139779</v>
+        <v>12.35946613672884</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.735179082636383</v>
+        <v>1.299761783296159</v>
       </c>
       <c r="C6" t="n">
-        <v>6.349050064622372</v>
+        <v>6.00935770926805</v>
       </c>
       <c r="D6" t="n">
-        <v>7.094725124518438</v>
+        <v>6.273746863451541</v>
       </c>
       <c r="E6" t="n">
-        <v>15.17895427177719</v>
+        <v>13.58286635601575</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.942556267940392</v>
+        <v>1.42283551249104</v>
       </c>
       <c r="C7" t="n">
-        <v>7.176944790682441</v>
+        <v>6.983097647397319</v>
       </c>
       <c r="D7" t="n">
-        <v>7.50744631772268</v>
+        <v>6.610300201389911</v>
       </c>
       <c r="E7" t="n">
-        <v>16.62694737634551</v>
+        <v>15.01623336127827</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.164319950132225</v>
+        <v>1.550814825260423</v>
       </c>
       <c r="C8" t="n">
-        <v>4.865975087659282</v>
+        <v>8.064049247691585</v>
       </c>
       <c r="D8" t="n">
-        <v>5.703958993776727</v>
+        <v>7.033922133940337</v>
       </c>
       <c r="E8" t="n">
-        <v>11.73425403156823</v>
+        <v>16.64878620689235</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.444804755488094</v>
+        <v>1.67598598499387</v>
       </c>
       <c r="C9" t="n">
-        <v>5.994857205830871</v>
+        <v>9.213911614501479</v>
       </c>
       <c r="D9" t="n">
-        <v>6.298244368963784</v>
+        <v>7.425803678577414</v>
       </c>
       <c r="E9" t="n">
-        <v>13.73790633028275</v>
+        <v>18.31570127807276</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.745265856900517</v>
+        <v>1.045885281765254</v>
       </c>
       <c r="C10" t="n">
-        <v>7.312621598822995</v>
+        <v>6.733110462558858</v>
       </c>
       <c r="D10" t="n">
-        <v>6.818712190476057</v>
+        <v>5.856988993811962</v>
       </c>
       <c r="E10" t="n">
-        <v>15.87659964619957</v>
+        <v>13.63598473813607</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.043809517540981</v>
+        <v>0.9803438050297375</v>
       </c>
       <c r="C11" t="n">
-        <v>8.780009438763026</v>
+        <v>7.008844122773617</v>
       </c>
       <c r="D11" t="n">
-        <v>7.365224125240915</v>
+        <v>5.713702916377139</v>
       </c>
       <c r="E11" t="n">
-        <v>18.18904308154492</v>
+        <v>13.70289084418049</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.35264578357677</v>
+        <v>1.062879334525767</v>
       </c>
       <c r="C12" t="n">
-        <v>10.32172208945266</v>
+        <v>8.168121264379376</v>
       </c>
       <c r="D12" t="n">
-        <v>7.992817101924273</v>
+        <v>6.13904510924207</v>
       </c>
       <c r="E12" t="n">
-        <v>20.6671849749537</v>
+        <v>15.37004570814721</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.657067113458278</v>
+        <v>0.8460112666576464</v>
       </c>
       <c r="C13" t="n">
-        <v>11.90641691591894</v>
+        <v>7.661784885914085</v>
       </c>
       <c r="D13" t="n">
-        <v>8.475665969294457</v>
+        <v>5.616107377097964</v>
       </c>
       <c r="E13" t="n">
-        <v>23.03914999867167</v>
+        <v>14.1239035296697</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.544082971762341</v>
+        <v>0.922322515708751</v>
       </c>
       <c r="C14" t="n">
-        <v>8.317238923177426</v>
+        <v>8.897265284323483</v>
       </c>
       <c r="D14" t="n">
-        <v>6.438900310550173</v>
+        <v>5.994001703416646</v>
       </c>
       <c r="E14" t="n">
-        <v>16.30022220548994</v>
+        <v>15.81358950344888</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.581114495166531</v>
+        <v>0.9006455263989815</v>
       </c>
       <c r="C15" t="n">
-        <v>9.006926502887852</v>
+        <v>9.555301318048993</v>
       </c>
       <c r="D15" t="n">
-        <v>6.491688884607524</v>
+        <v>6.066700120916123</v>
       </c>
       <c r="E15" t="n">
-        <v>17.07972988266191</v>
+        <v>16.5226469653641</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.836467073041126</v>
+        <v>0.9924978416083131</v>
       </c>
       <c r="C16" t="n">
-        <v>10.70384795724734</v>
+        <v>11.16245176233215</v>
       </c>
       <c r="D16" t="n">
-        <v>6.955319237938081</v>
+        <v>6.488468752137594</v>
       </c>
       <c r="E16" t="n">
-        <v>19.49563426822655</v>
+        <v>18.64341835607805</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.472709913663598</v>
+        <v>0.6002110939453725</v>
       </c>
       <c r="C17" t="n">
-        <v>9.963747632923837</v>
+        <v>8.417553903597366</v>
       </c>
       <c r="D17" t="n">
-        <v>6.456925198400145</v>
+        <v>5.412257283788155</v>
       </c>
       <c r="E17" t="n">
-        <v>17.89338274498758</v>
+        <v>14.43002228133089</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.676589459404533</v>
+        <v>0.4713665252400211</v>
       </c>
       <c r="C18" t="n">
-        <v>11.72471830750838</v>
+        <v>7.395122574486566</v>
       </c>
       <c r="D18" t="n">
-        <v>6.923638239522035</v>
+        <v>4.951366006552449</v>
       </c>
       <c r="E18" t="n">
-        <v>20.32494600643495</v>
+        <v>12.81785510627904</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.676461832202981</v>
+        <v>0.5570632823437253</v>
       </c>
       <c r="C19" t="n">
-        <v>12.65253861036092</v>
+        <v>9.176837578061848</v>
       </c>
       <c r="D19" t="n">
-        <v>7.036225066245061</v>
+        <v>5.475992344747859</v>
       </c>
       <c r="E19" t="n">
-        <v>21.36522550880896</v>
+        <v>15.20989320515343</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.859292707164865</v>
+        <v>0.6411499732124645</v>
       </c>
       <c r="C20" t="n">
-        <v>14.58578637208669</v>
+        <v>11.05273163890553</v>
       </c>
       <c r="D20" t="n">
-        <v>7.575361635509238</v>
+        <v>5.961515671883119</v>
       </c>
       <c r="E20" t="n">
-        <v>24.0204407147608</v>
+        <v>17.65539728400111</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.101570011550134</v>
+        <v>0.7165187444674921</v>
       </c>
       <c r="C21" t="n">
-        <v>10.74676014939996</v>
+        <v>13.01172082543665</v>
       </c>
       <c r="D21" t="n">
-        <v>6.340902254712257</v>
+        <v>6.443877771410705</v>
       </c>
       <c r="E21" t="n">
-        <v>18.18923241566236</v>
+        <v>20.17211734131485</v>
       </c>
     </row>
   </sheetData>
